--- a/АБК/Том СОТС АБК/Протокол сопротивления изоляции СОТС АБК (образец и бланк).xlsx
+++ b/АБК/Том СОТС АБК/Протокол сопротивления изоляции СОТС АБК (образец и бланк).xlsx
@@ -608,7 +608,7 @@
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Исполнительная документация: 16/1/26-ИД-АБК, лист 7; кабельный журнал 16/1/26-ИД-АБК.КЖ (раздел СОТС). Рабочая документация 16/1/26-СОТС-Р.</t>
+          <t>Исполнительная документация: 16/1/26-СОТС-ИД-АБК, лист 2; кабельный журнал 16/1/26-СОТС-ИД-АБК.КЖ. Рабочая документация 16/1/26-СОТС-Р.</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Исполнительная документация: 16/1/26-ИД-АБК, лист 7; кабельный журнал 16/1/26-ИД-АБК.КЖ (раздел СОТС). Рабочая документация 16/1/26-СОТС-Р.</t>
+          <t>Исполнительная документация: 16/1/26-СОТС-ИД-АБК, лист 2; кабельный журнал 16/1/26-СОТС-ИД-АБК.КЖ. Рабочая документация 16/1/26-СОТС-Р.</t>
         </is>
       </c>
     </row>
